--- a/VibeProject1/Assets/Table/Tactics/RoleGroupTactics.xlsx
+++ b/VibeProject1/Assets/Table/Tactics/RoleGroupTactics.xlsx
@@ -435,27 +435,39 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -490,66 +502,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DeepestPenetration</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HighestHpRatio</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HighestAttack</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LowestHp</t>
+        </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -587,66 +623,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ApproachAttack</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Surround</t>
+        </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Disperse</t>
+        </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -684,44 +744,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resilient</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FallBackOnHeavyDamage</t>
+        </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kiting</t>
+        </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RangedDealer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RetreatOnHit</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -754,8 +830,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -764,8 +842,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DeepestPenetration</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -774,8 +854,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HighestHpRatio</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -784,8 +866,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HighestAttack</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -794,8 +878,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LowestHp</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -830,8 +916,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ApproachAttack</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -840,8 +928,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -850,8 +940,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Blocking</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -860,8 +952,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -870,8 +964,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Surround</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -880,8 +976,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Disperse</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -916,8 +1014,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Resilient</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -926,8 +1026,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FallBackOnHeavyDamage</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -936,8 +1038,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kiting</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -946,8 +1050,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RetreatOnHit</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
